--- a/hourly datasets/cap_gen_year4final.xlsx
+++ b/hourly datasets/cap_gen_year4final.xlsx
@@ -485,7 +485,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.09640014858912448</v>
+        <v>0.09355855325255041</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1042360274185795</v>
+        <v>0.100862707589604</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +503,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.2006361760077039</v>
+        <v>0.1944212608421544</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1327415693877952</v>
+        <v>0.130842214015385</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +521,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.2291417179769197</v>
+        <v>0.2244007672679355</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05557451227918586</v>
+        <v>0.04954078782690678</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -539,7 +539,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.1519746608683104</v>
+        <v>0.1430993410794572</v>
       </c>
     </row>
     <row r="6">
@@ -549,25 +549,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04807634347780593</v>
+        <v>0.03958684647534404</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00483549525424892</v>
+        <v>0.002525802345685106</v>
       </c>
       <c r="D6" t="n">
-        <v>6.608260337980272</v>
+        <v>6.742860493120867</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01974750449272871</v>
+        <v>0.01065269294542749</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03857812139835367</v>
+        <v>0.03463352981535368</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05757456555725905</v>
+        <v>0.04454016313533513</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1444764920669304</v>
+        <v>0.1331453997278945</v>
       </c>
     </row>
     <row r="7">
@@ -577,25 +577,15 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03666292457026844</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.004477224564120189</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3.507778098800936</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.02329402308806026</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.0278539889973731</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.045471860143165</v>
-      </c>
+        <v>0.02616405509405232</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>0.1330630731593929</v>
+        <v>0.1197226083466027</v>
       </c>
     </row>
     <row r="8">
@@ -605,25 +595,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0324564869705281</v>
+        <v>0.02264363570466791</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003516804698453915</v>
+        <v>0.001180937142560304</v>
       </c>
       <c r="D8" t="n">
-        <v>3.251608481702725</v>
+        <v>3.056360369477982</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01987996194583503</v>
+        <v>0.01099942753327114</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02554780295339812</v>
+        <v>0.02032785851060925</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03936517098765764</v>
+        <v>0.02495941289872727</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1288566355596526</v>
+        <v>0.1162021889572183</v>
       </c>
     </row>
     <row r="9">
@@ -633,25 +623,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03776673540075415</v>
+        <v>0.02385637766348525</v>
       </c>
       <c r="C9" t="n">
-        <v>0.004015835282486879</v>
+        <v>0.001700407734268352</v>
       </c>
       <c r="D9" t="n">
-        <v>3.783227656605955</v>
+        <v>3.377293537486873</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01204012986149713</v>
+        <v>0.008397134716921729</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02987344789083541</v>
+        <v>0.02051698725865643</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0456600229106744</v>
+        <v>0.02719576806831366</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1341668839898786</v>
+        <v>0.1174149309160357</v>
       </c>
     </row>
     <row r="10">
@@ -661,25 +651,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.03063983820585928</v>
+        <v>0.01647143985495271</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00343710494745291</v>
+        <v>0.0009070020627838719</v>
       </c>
       <c r="D10" t="n">
-        <v>3.200323776621989</v>
+        <v>2.785463148214779</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01224433255601132</v>
+        <v>0.006040004751772889</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02388544852430685</v>
+        <v>0.01469293669255</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03739422788741251</v>
+        <v>0.01824994301735478</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1270399867949838</v>
+        <v>0.1100299931075031</v>
       </c>
     </row>
     <row r="11">
@@ -689,7 +679,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03041860034738776</v>
+        <v>0.02690739188919336</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -697,7 +687,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1268187489365122</v>
+        <v>0.1204659451417438</v>
       </c>
     </row>
     <row r="12">
@@ -707,7 +697,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04662430579991968</v>
+        <v>0.04427608920922066</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -715,7 +705,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1430244543890442</v>
+        <v>0.1378346424617711</v>
       </c>
     </row>
     <row r="13">
@@ -725,7 +715,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05929880620547275</v>
+        <v>0.05532076255337438</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -733,7 +723,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1556989547945972</v>
+        <v>0.1488793158059248</v>
       </c>
     </row>
     <row r="14">
@@ -743,7 +733,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06313924993060988</v>
+        <v>0.05867381080765822</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -751,7 +741,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1595393985197344</v>
+        <v>0.1522323640602086</v>
       </c>
     </row>
     <row r="15">
@@ -761,7 +751,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06908009376956847</v>
+        <v>0.06411491389693816</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -769,7 +759,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.165480242358693</v>
+        <v>0.1576734671494886</v>
       </c>
     </row>
     <row r="16">
@@ -779,7 +769,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.07013845731300106</v>
+        <v>0.06604292716272618</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -787,7 +777,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1665386059021255</v>
+        <v>0.1596014804152766</v>
       </c>
     </row>
     <row r="17">
@@ -797,7 +787,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.07314807562362598</v>
+        <v>0.06906377487709073</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -805,7 +795,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1695482242127505</v>
+        <v>0.1626223281296411</v>
       </c>
     </row>
     <row r="18">
@@ -815,22 +805,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.09640014858912448</v>
+        <v>-0.09355855325255041</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0122303611188648</v>
+        <v>0.01112669510834599</v>
       </c>
       <c r="D18" t="n">
-        <v>-17.20231439914257</v>
+        <v>-17.32267136833488</v>
       </c>
       <c r="E18" t="n">
-        <v>0.06297925392800259</v>
+        <v>0.06032126250931887</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1205017252643247</v>
+        <v>-0.1154670499125041</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0722985719139239</v>
+        <v>-0.07165005659259689</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -843,7 +833,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.07642607716927302</v>
+        <v>0.07198066540955982</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -851,7 +841,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1728262257583975</v>
+        <v>0.1655392186621102</v>
       </c>
     </row>
     <row r="20">
@@ -861,25 +851,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.08127681172355231</v>
+        <v>0.07758889123533735</v>
       </c>
       <c r="C20" t="n">
-        <v>0.01007387060976619</v>
+        <v>0.009030272616000539</v>
       </c>
       <c r="D20" t="n">
-        <v>16.69061209008504</v>
+        <v>16.5108943963146</v>
       </c>
       <c r="E20" t="n">
-        <v>0.04909126925379184</v>
+        <v>0.04970951419633877</v>
       </c>
       <c r="F20" t="n">
-        <v>0.06142199449032846</v>
+        <v>0.05981138574583768</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1011316289567763</v>
+        <v>0.09536639672483718</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1776769603126768</v>
+        <v>0.1711474444878878</v>
       </c>
     </row>
     <row r="21">
@@ -889,7 +879,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.08462383564843402</v>
+        <v>0.08029809455906622</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -897,7 +887,7 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.1810239842375585</v>
+        <v>0.1738566478116166</v>
       </c>
     </row>
     <row r="22">
@@ -907,25 +897,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.08721080934262318</v>
+        <v>0.08369956235206256</v>
       </c>
       <c r="C22" t="n">
-        <v>0.01051495079948699</v>
+        <v>0.009123255462571157</v>
       </c>
       <c r="D22" t="n">
-        <v>16.28591936377417</v>
+        <v>16.27400742669092</v>
       </c>
       <c r="E22" t="n">
-        <v>0.05111023187141769</v>
+        <v>0.04973807441996544</v>
       </c>
       <c r="F22" t="n">
-        <v>0.06646040862272151</v>
+        <v>0.06572814065354306</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1079612100625253</v>
+        <v>0.1016709840505822</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1836109579317476</v>
+        <v>0.177258115604613</v>
       </c>
     </row>
     <row r="23">
@@ -935,25 +925,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.09132598976443784</v>
+        <v>0.08804537033317096</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0110112893770334</v>
+        <v>0.009925238796621341</v>
       </c>
       <c r="D23" t="n">
-        <v>3218145331650.303</v>
+        <v>3126064529870.92</v>
       </c>
       <c r="E23" t="n">
-        <v>0.05836741945072728</v>
+        <v>0.06040413684718463</v>
       </c>
       <c r="F23" t="n">
-        <v>0.06958191521043852</v>
+        <v>0.06844491822777703</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1130700643184372</v>
+        <v>0.107645822438565</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1877261383535623</v>
+        <v>0.1816039235857214</v>
       </c>
     </row>
     <row r="24">
@@ -963,25 +953,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.08908402062988305</v>
+        <v>0.08635652268292975</v>
       </c>
       <c r="C24" t="n">
-        <v>0.01087746673390756</v>
+        <v>0.009916276703609145</v>
       </c>
       <c r="D24" t="n">
-        <v>13.99310405047447</v>
+        <v>14.07868020055008</v>
       </c>
       <c r="E24" t="n">
-        <v>0.06595513263659947</v>
+        <v>0.0669388518647378</v>
       </c>
       <c r="F24" t="n">
-        <v>0.06759855770788888</v>
+        <v>0.06676490002754976</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1105694835518773</v>
+        <v>0.1059481453383101</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1854841692190075</v>
+        <v>0.1799150759354802</v>
       </c>
     </row>
     <row r="25">
@@ -991,25 +981,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.08947289932199931</v>
+        <v>0.08590100219380485</v>
       </c>
       <c r="C25" t="n">
-        <v>0.01060687481264844</v>
+        <v>0.009455615718496086</v>
       </c>
       <c r="D25" t="n">
-        <v>12.76293819123774</v>
+        <v>12.72938653059315</v>
       </c>
       <c r="E25" t="n">
-        <v>0.070611966486368</v>
+        <v>0.07255774457766342</v>
       </c>
       <c r="F25" t="n">
-        <v>0.06858118500825905</v>
+        <v>0.06728365366859805</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1103646136357392</v>
+        <v>0.1045183507190114</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1858730479111238</v>
+        <v>0.1794595554463553</v>
       </c>
     </row>
     <row r="26">
@@ -1019,25 +1009,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.09491631149826743</v>
+        <v>0.09069101156141578</v>
       </c>
       <c r="C26" t="n">
-        <v>0.01110838118191226</v>
+        <v>0.009975799536118784</v>
       </c>
       <c r="D26" t="n">
-        <v>12.84564315253356</v>
+        <v>12.86253217052124</v>
       </c>
       <c r="E26" t="n">
-        <v>0.07355619123896143</v>
+        <v>0.07354396894161391</v>
       </c>
       <c r="F26" t="n">
-        <v>0.07301442864616031</v>
+        <v>0.07102464556497859</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1168181943503741</v>
+        <v>0.1103573775578537</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1913164600873919</v>
+        <v>0.1842495648139662</v>
       </c>
     </row>
     <row r="27">
@@ -1047,25 +1037,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.09465985696319772</v>
+        <v>0.09038876253183947</v>
       </c>
       <c r="C27" t="n">
-        <v>0.01110201127043648</v>
+        <v>0.01005024638042946</v>
       </c>
       <c r="D27" t="n">
-        <v>11.73945612444291</v>
+        <v>11.80427516126105</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0758936972211408</v>
+        <v>0.07450033059719843</v>
       </c>
       <c r="F27" t="n">
-        <v>0.07277628112562902</v>
+        <v>0.07058358600021261</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1165434328007666</v>
+        <v>0.1101939390634663</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1910600055523222</v>
+        <v>0.1839473157843899</v>
       </c>
     </row>
     <row r="28">
@@ -1075,25 +1065,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1040658556852016</v>
+        <v>0.09985957022071371</v>
       </c>
       <c r="C28" t="n">
-        <v>0.01128497505878369</v>
+        <v>0.01011203765299126</v>
       </c>
       <c r="D28" t="n">
-        <v>11.61687582407435</v>
+        <v>11.84801185464836</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1250278914080156</v>
+        <v>0.1234511335313466</v>
       </c>
       <c r="F28" t="n">
-        <v>0.08183407517647785</v>
+        <v>0.07994711088236757</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1262976361939254</v>
+        <v>0.1197720295590605</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2004660042743261</v>
+        <v>0.1934181234732641</v>
       </c>
     </row>
     <row r="29">
@@ -1103,25 +1093,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.03635591221195728</v>
+        <v>0.02141475695924925</v>
       </c>
       <c r="C29" t="n">
-        <v>0.003889794707221325</v>
+        <v>0.001203378944246972</v>
       </c>
       <c r="D29" t="n">
-        <v>5.332568551475089</v>
+        <v>4.687520420292651</v>
       </c>
       <c r="E29" t="n">
-        <v>0.01785822230520033</v>
+        <v>0.007069669675996587</v>
       </c>
       <c r="F29" t="n">
-        <v>0.02870167976068788</v>
+        <v>0.01905554468333879</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0440101446632265</v>
+        <v>0.02377396923515974</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1327560608010818</v>
+        <v>0.1149733102117997</v>
       </c>
     </row>
   </sheetData>

--- a/hourly datasets/cap_gen_year4final.xlsx
+++ b/hourly datasets/cap_gen_year4final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>first_seen_iter</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>coef_pos</t>
         </is>
       </c>
@@ -477,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.2185766315918744</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -485,7 +490,10 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.09355855325255041</v>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.09230913639674804</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +503,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.100862707589604</v>
+        <v>0.3592821884998787</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +511,10 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.1944212608421544</v>
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2330146933047524</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +524,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.130842214015385</v>
+        <v>0.3698641502654554</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +532,10 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.2244007672679355</v>
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.243596655070329</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +545,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04954078782690678</v>
+        <v>0.3983749103292717</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -539,7 +553,10 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.1430993410794572</v>
+        <v>9</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2721074151341454</v>
       </c>
     </row>
     <row r="6">
@@ -549,25 +566,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03958684647534404</v>
+        <v>0.325484879976691</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002525802345685106</v>
+        <v>0.007234637121918138</v>
       </c>
       <c r="D6" t="n">
-        <v>6.742860493120867</v>
+        <v>25.5964526503829</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01065269294542749</v>
+        <v>0.01122524682490844</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03463352981535368</v>
+        <v>0.1458341963952905</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04454016313533513</v>
+        <v>0.1742057706054407</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1331453997278945</v>
+        <v>26</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1992173847815647</v>
       </c>
     </row>
     <row r="7">
@@ -577,7 +597,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02616405509405232</v>
+        <v>0.3145705546180504</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -585,7 +605,10 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>0.1197226083466027</v>
+        <v>26</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1883030594229241</v>
       </c>
     </row>
     <row r="8">
@@ -595,25 +618,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02264363570466791</v>
+        <v>0.3126778101374382</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001180937142560304</v>
+        <v>0.006861209813508659</v>
       </c>
       <c r="D8" t="n">
-        <v>3.056360369477982</v>
+        <v>25.58247439638313</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01099942753327114</v>
+        <v>0.01165633109377003</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02032785851060925</v>
+        <v>0.1589055279169359</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02495941289872727</v>
+        <v>0.1858109777839286</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1162021889572183</v>
+        <v>26</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1864103149423118</v>
       </c>
     </row>
     <row r="9">
@@ -623,25 +649,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02385637766348525</v>
+        <v>0.2690457381474581</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001700407734268352</v>
+        <v>0.008844720695855198</v>
       </c>
       <c r="D9" t="n">
-        <v>3.377293537486873</v>
+        <v>16.03393650134726</v>
       </c>
       <c r="E9" t="n">
-        <v>0.008397134716921729</v>
+        <v>0.008720293075397562</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02051698725865643</v>
+        <v>0.1180636250678258</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02719576806831366</v>
+        <v>0.1528266286455022</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1174149309160357</v>
+        <v>17</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1427782429523318</v>
       </c>
     </row>
     <row r="10">
@@ -651,25 +680,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01647143985495271</v>
+        <v>0.309904933883886</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0009070020627838719</v>
+        <v>0.006743886967172915</v>
       </c>
       <c r="D10" t="n">
-        <v>2.785463148214779</v>
+        <v>26.10840346640106</v>
       </c>
       <c r="E10" t="n">
-        <v>0.006040004751772889</v>
+        <v>0.006379093428914972</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01469293669255</v>
+        <v>0.1578793934873498</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01824994301735478</v>
+        <v>0.1843243942278507</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1100299931075031</v>
+        <v>26</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1836374386887596</v>
       </c>
     </row>
     <row r="11">
@@ -679,7 +711,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02690739188919336</v>
+        <v>0.2592969806881756</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -687,7 +719,10 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1204659451417438</v>
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1330294854930493</v>
       </c>
     </row>
     <row r="12">
@@ -697,7 +732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04427608920922066</v>
+        <v>0.2779111183648396</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -705,7 +740,10 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1378346424617711</v>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1516436231697133</v>
       </c>
     </row>
     <row r="13">
@@ -715,7 +753,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05532076255337438</v>
+        <v>0.291581111318574</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -723,7 +761,10 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1488793158059248</v>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1653136161234477</v>
       </c>
     </row>
     <row r="14">
@@ -733,7 +774,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05867381080765822</v>
+        <v>0.2985203300851136</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -741,7 +782,10 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1522323640602086</v>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1722528348899873</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +795,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06411491389693816</v>
+        <v>0.3048076432607287</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -759,7 +803,10 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1576734671494886</v>
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1785401480656023</v>
       </c>
     </row>
     <row r="16">
@@ -769,7 +816,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06604292716272618</v>
+        <v>0.3104661634628167</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -777,7 +824,10 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1596014804152766</v>
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1841986682676904</v>
       </c>
     </row>
     <row r="17">
@@ -787,7 +837,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.06906377487709073</v>
+        <v>0.3136675989614612</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -795,7 +845,10 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1626223281296411</v>
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1874001037663349</v>
       </c>
     </row>
     <row r="18">
@@ -805,24 +858,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.09355855325255041</v>
+        <v>0.1262674951951263</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01112669510834599</v>
+        <v>0.01096298238109893</v>
       </c>
       <c r="D18" t="n">
-        <v>-17.32267136833488</v>
+        <v>-17.26058608256109</v>
       </c>
       <c r="E18" t="n">
-        <v>0.06032126250931887</v>
+        <v>0.05795754556569745</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1154670499125041</v>
+        <v>-0.1146732578819173</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.07165005659259689</v>
+        <v>-0.07149975714967409</v>
       </c>
       <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -833,7 +889,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.07198066540955982</v>
+        <v>0.3175915240998547</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -841,7 +897,10 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1655392186621102</v>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.1913240289047284</v>
       </c>
     </row>
     <row r="20">
@@ -851,25 +910,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.07758889123533735</v>
+        <v>0.3206531078068824</v>
       </c>
       <c r="C20" t="n">
-        <v>0.009030272616000539</v>
+        <v>0.009003404384403413</v>
       </c>
       <c r="D20" t="n">
-        <v>16.5108943963146</v>
+        <v>16.46818544392715</v>
       </c>
       <c r="E20" t="n">
-        <v>0.04970951419633877</v>
+        <v>0.04966639162839847</v>
       </c>
       <c r="F20" t="n">
-        <v>0.05981138574583768</v>
+        <v>0.05948378490124061</v>
       </c>
       <c r="G20" t="n">
-        <v>0.09536639672483718</v>
+        <v>0.09493308316705201</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1711474444878878</v>
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.194385612611756</v>
       </c>
     </row>
     <row r="21">
@@ -879,7 +941,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.08029809455906622</v>
+        <v>0.3237652484475209</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -887,7 +949,10 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.1738566478116166</v>
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.1974977532523945</v>
       </c>
     </row>
     <row r="22">
@@ -897,25 +962,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.08369956235206256</v>
+        <v>0.3261541762987791</v>
       </c>
       <c r="C22" t="n">
-        <v>0.009123255462571157</v>
+        <v>0.009090747434926688</v>
       </c>
       <c r="D22" t="n">
-        <v>16.27400742669092</v>
+        <v>16.21149815031513</v>
       </c>
       <c r="E22" t="n">
-        <v>0.04973807441996544</v>
+        <v>0.0496609229531256</v>
       </c>
       <c r="F22" t="n">
-        <v>0.06572814065354306</v>
+        <v>0.06524771635512959</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1016709840505822</v>
+        <v>0.101062592342708</v>
       </c>
       <c r="H22" t="n">
-        <v>0.177258115604613</v>
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.1998866811036527</v>
       </c>
     </row>
     <row r="23">
@@ -925,25 +993,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.08804537033317096</v>
+        <v>0.3311009401094073</v>
       </c>
       <c r="C23" t="n">
-        <v>0.009925238796621341</v>
+        <v>0.009877953404221745</v>
       </c>
       <c r="D23" t="n">
-        <v>3126064529870.92</v>
+        <v>3125912436338.943</v>
       </c>
       <c r="E23" t="n">
-        <v>0.06040413684718463</v>
+        <v>0.06020835057094938</v>
       </c>
       <c r="F23" t="n">
-        <v>0.06844491822777703</v>
+        <v>0.06763753998916379</v>
       </c>
       <c r="G23" t="n">
-        <v>0.107645822438565</v>
+        <v>0.1066522158401739</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1816039235857214</v>
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.204833444914281</v>
       </c>
     </row>
     <row r="24">
@@ -953,25 +1024,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.08635652268292975</v>
+        <v>0.3363292717896332</v>
       </c>
       <c r="C24" t="n">
-        <v>0.009916276703609145</v>
+        <v>0.009873954400962398</v>
       </c>
       <c r="D24" t="n">
-        <v>14.07868020055008</v>
+        <v>14.02893643597682</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0669388518647378</v>
+        <v>0.06661111737753812</v>
       </c>
       <c r="F24" t="n">
-        <v>0.06676490002754976</v>
+        <v>0.06640052497254099</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1059481453383101</v>
+        <v>0.1054165500077412</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1799150759354802</v>
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2100617765945068</v>
       </c>
     </row>
     <row r="25">
@@ -981,25 +1055,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.08590100219380485</v>
+        <v>0.3386723980197088</v>
       </c>
       <c r="C25" t="n">
-        <v>0.009455615718496086</v>
+        <v>0.009387076406438514</v>
       </c>
       <c r="D25" t="n">
-        <v>12.72938653059315</v>
+        <v>12.61819978330064</v>
       </c>
       <c r="E25" t="n">
-        <v>0.07255774457766342</v>
+        <v>0.07200541455560298</v>
       </c>
       <c r="F25" t="n">
-        <v>0.06728365366859805</v>
+        <v>0.06647731129813482</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1045183507190114</v>
+        <v>0.1034419528917955</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1794595554463553</v>
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.2124049028245825</v>
       </c>
     </row>
     <row r="26">
@@ -1009,25 +1086,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.09069101156141578</v>
+        <v>0.3445780933102892</v>
       </c>
       <c r="C26" t="n">
-        <v>0.009975799536118784</v>
+        <v>0.009882932593437102</v>
       </c>
       <c r="D26" t="n">
-        <v>12.86253217052124</v>
+        <v>12.73521679373454</v>
       </c>
       <c r="E26" t="n">
-        <v>0.07354396894161391</v>
+        <v>0.07301675136853641</v>
       </c>
       <c r="F26" t="n">
-        <v>0.07102464556497859</v>
+        <v>0.07003800035039708</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1103573775578537</v>
+        <v>0.1090044758338046</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1842495648139662</v>
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2183105981151628</v>
       </c>
     </row>
     <row r="27">
@@ -1037,25 +1117,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.09038876253183947</v>
+        <v>0.3415081160781983</v>
       </c>
       <c r="C27" t="n">
-        <v>0.01005024638042946</v>
+        <v>0.009804050559029453</v>
       </c>
       <c r="D27" t="n">
-        <v>11.80427516126105</v>
+        <v>11.47514719702682</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07450033059719843</v>
+        <v>0.07400084548859015</v>
       </c>
       <c r="F27" t="n">
-        <v>0.07058358600021261</v>
+        <v>0.06698950662392021</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1101939390634663</v>
+        <v>0.1056318567291104</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1839473157843899</v>
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2152406208830719</v>
       </c>
     </row>
     <row r="28">
@@ -1065,25 +1148,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.09985957022071371</v>
+        <v>0.3586124647433439</v>
       </c>
       <c r="C28" t="n">
-        <v>0.01011203765299126</v>
+        <v>0.0101207175136376</v>
       </c>
       <c r="D28" t="n">
-        <v>11.84801185464836</v>
+        <v>11.85818182190557</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1234511335313466</v>
+        <v>0.1235571001695709</v>
       </c>
       <c r="F28" t="n">
-        <v>0.07994711088236757</v>
+        <v>0.08001573501188033</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1197720295590605</v>
+        <v>0.119874838168124</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1934181234732641</v>
+        <v>2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2323449695482175</v>
       </c>
     </row>
     <row r="29">
@@ -1093,25 +1179,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.02141475695924925</v>
+        <v>0.3187132021956692</v>
       </c>
       <c r="C29" t="n">
-        <v>0.001203378944246972</v>
+        <v>0.006368127061751046</v>
       </c>
       <c r="D29" t="n">
-        <v>4.687520420292651</v>
+        <v>25.93943151221366</v>
       </c>
       <c r="E29" t="n">
-        <v>0.007069669675996587</v>
+        <v>0.00743029632275179</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01905554468333879</v>
+        <v>0.1466754688572238</v>
       </c>
       <c r="G29" t="n">
-        <v>0.02377396923515974</v>
+        <v>0.1716462381376008</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1149733102117997</v>
+        <v>26</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.1924457070005428</v>
       </c>
     </row>
   </sheetData>
